--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>101693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552522.3859772705</v>
+        <v>552522</v>
       </c>
       <c r="R2" t="n">
-        <v>6295791.565088866</v>
+        <v>6295792</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552522.3859772705</v>
+        <v>552522</v>
       </c>
       <c r="R3" t="n">
-        <v>6295791.565088866</v>
+        <v>6295792</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104062</v>
+        <v>104071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104071</v>
+        <v>104074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104074</v>
+        <v>104101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104101</v>
+        <v>104107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104107</v>
+        <v>104114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98648</v>
+        <v>98655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104114</v>
+        <v>104118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98655</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104118</v>
+        <v>104125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104128</v>
+        <v>104133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104133</v>
+        <v>104141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98674</v>
+        <v>98682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74462690</v>
       </c>
       <c r="B2" t="n">
-        <v>104141</v>
+        <v>104151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74567318</v>
       </c>
       <c r="B3" t="n">
-        <v>98682</v>
+        <v>98692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74462690</v>
+        <v>74567318</v>
       </c>
       <c r="B2" t="n">
-        <v>104151</v>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224417</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk solvända</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. obscurum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Celak.) Holub</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Köpstaden, SV om bäcken, Sm</t>
+          <t>30 Köpstaden, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G9a 2333. SOM: Helianthemum nummularium ssp. obscurum. LEG: Jan-Erik Hederås, Anna-Brita Carlander, Bengt Örneberg</t>
+          <t>Smålands flora 2007: KOO: 4G9a 2333. SOM: Listera ovata. LEG: Jan-Erik Hederås, Anna-Brita Carlander, Bengt Örneberg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Ängslövskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,38 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74567318</v>
+        <v>74462690</v>
       </c>
       <c r="B3" t="n">
-        <v>98692</v>
+        <v>104641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>224417</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mörk solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Helianthemum nummularium subsp. obscurum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Celak.) Holub</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>30 Köpstaden, Sm</t>
+          <t>Köpstaden, SV om bäcken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G9a 2333. SOM: Listera ovata. LEG: Jan-Erik Hederås, Anna-Brita Carlander, Bengt Örneberg</t>
+          <t>Smålands flora 2007: KOO: 4G9a 2333. SOM: Helianthemum nummularium ssp. obscurum. LEG: Jan-Erik Hederås, Anna-Brita Carlander, Bengt Örneberg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Ängslövskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 51784-2023 artfynd.xlsx
+++ b/artfynd/A 51784-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74567318</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74462690</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>